--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -33849,7 +33849,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-01 15:38</t>
+          <t>2026-06-02 13:39</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -33933,7 +33933,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-03 15:06</t>
+          <t>2026-06-03 16:40</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -33933,7 +33933,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-03 16:40</t>
+          <t>2026-06-03 17:30</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34269,7 +34269,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-04 13:12</t>
+          <t>2026-06-04 13:19</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34269,7 +34269,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-04 13:19</t>
+          <t>2026-06-04 13:38</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34353,7 +34353,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-05 12:54</t>
+          <t>2026-06-05 13:31</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34605,7 +34605,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-06 12:20</t>
+          <t>2026-06-06 12:29</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34605,7 +34605,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-06 12:29</t>
+          <t>2026-06-07 10:00</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -34941,7 +34941,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-08 20:47</t>
+          <t>2026-06-09 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -35361,7 +35361,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-10 10:20</t>
+          <t>2026-06-11 10:02</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -35361,7 +35361,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-12 10:04</t>
+          <t>2026-06-13 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -35697,7 +35697,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-15 10:01</t>
+          <t>2026-06-16 10:02</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -37041,7 +37041,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-22 10:01</t>
+          <t>2026-06-23 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -38049,7 +38049,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-27 10:00</t>
+          <t>2026-06-28 10:01</t>
         </is>
       </c>
     </row>

--- a/2026 Batting Stats/mlb_batting_stats.xlsx
+++ b/2026 Batting Stats/mlb_batting_stats.xlsx
@@ -38385,7 +38385,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-06-29 10:00</t>
+          <t>2026-06-30 10:01</t>
         </is>
       </c>
     </row>
